--- a/excelAvancado/aula07/Planilha_Funcoes_Texto_Excel.xlsx
+++ b/excelAvancado/aula07/Planilha_Funcoes_Texto_Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\excelAvancado\aula07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6154C4BE-BB3E-4080-8F72-501FF867F95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E231A9-0572-42EF-899F-0EED0DBFA377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
